--- a/技术文档/缺陷管理表.xlsx
+++ b/技术文档/缺陷管理表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="123">
   <si>
     <t>DDL缺陷提交表</t>
   </si>
@@ -294,7 +294,7 @@
     <t>bug013</t>
   </si>
   <si>
-    <t>导入数据，没有成功创建任务</t>
+    <t>点击导入数据，没有成功创建任务</t>
   </si>
   <si>
     <t>数据处理</t>
@@ -317,6 +317,9 @@
     <t>开启邮件提醒临期任务，未成功发送邮件</t>
   </si>
   <si>
+    <t>fixing</t>
+  </si>
+  <si>
     <t>邮件提醒</t>
   </si>
   <si>
@@ -357,6 +360,9 @@
     <t>目标无法打开查看</t>
   </si>
   <si>
+    <t>已修复</t>
+  </si>
+  <si>
     <t>查看</t>
   </si>
   <si>
@@ -369,6 +375,62 @@
   </si>
   <si>
     <t>不能查看</t>
+  </si>
+  <si>
+    <t>bug017</t>
+  </si>
+  <si>
+    <t>语音识别失败</t>
+  </si>
+  <si>
+    <t>语音</t>
+  </si>
+  <si>
+    <t>1.点击右下角“+”
+2.点击语音按钮</t>
+  </si>
+  <si>
+    <t>可以语音识别</t>
+  </si>
+  <si>
+    <t>不能</t>
+  </si>
+  <si>
+    <t>bug018</t>
+  </si>
+  <si>
+    <t>ai解析时输入多个任务，没有分别创建</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>1.点击右下角“+”
+2.ai智能解析输入：完成本周三个紧急报告：财务分析，市场调研，竞品分析，周五前完成
+3.点击智能解析</t>
+  </si>
+  <si>
+    <t>可以自动识别出三个任务</t>
+  </si>
+  <si>
+    <t>识别成了一个</t>
+  </si>
+  <si>
+    <t>bug019</t>
+  </si>
+  <si>
+    <t>ai解析时无法识别开始时间</t>
+  </si>
+  <si>
+    <t>1.点击右下角“+”
+2.ai智能解析输入：今天晚上六点到七点吃饭
+3.点击智能解析</t>
+  </si>
+  <si>
+    <t>可以自动识别出开始时间和截止时间</t>
+  </si>
+  <si>
+    <t>只能识别截止时间</t>
   </si>
 </sst>
 </file>
@@ -381,7 +443,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,6 +462,13 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -912,133 +981,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1067,8 +1136,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1476,15 +1545,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>837565</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>403225</xdr:rowOff>
+      <xdr:colOff>1813560</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>469265</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>2875915</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>150495</xdr:rowOff>
+      <xdr:colOff>3299460</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>201930</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1501,8 +1570,50 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16341090" y="11890375"/>
-          <a:ext cx="2038350" cy="3303270"/>
+          <a:off x="17317085" y="11245215"/>
+          <a:ext cx="1485900" cy="2399665"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>309880</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1877060</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15663545" y="12863830"/>
+          <a:ext cx="1717040" cy="3452495"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1768,7 +1879,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="68.4363636363636" style="1" customWidth="1"/>
@@ -2121,7 +2232,7 @@
         <v>72</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>15</v>
@@ -2193,7 +2304,7 @@
       <c r="F15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="6" t="s">
         <v>83</v>
       </c>
       <c r="H15" s="1" t="s">
@@ -2211,7 +2322,7 @@
         <v>87</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>15</v>
@@ -2220,24 +2331,24 @@
         <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G16" s="8" t="s">
         <v>89</v>
       </c>
+      <c r="G16" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="H16" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" ht="42" spans="1:9">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>22</v>
@@ -2249,46 +2360,136 @@
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="8" t="s">
         <v>95</v>
       </c>
+      <c r="G17" s="6" t="s">
+        <v>96</v>
+      </c>
       <c r="H17" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" ht="42" spans="1:9">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:9">
+      <c r="A19" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>103</v>
-      </c>
+      <c r="D19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" ht="70" spans="1:9">
+      <c r="A20" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" ht="56" spans="1:9">
+      <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="11:11">
+      <c r="K33" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
